--- a/stories/arbres/ATOM-FAM.AID.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1289,6 +1305,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dorian est dans sa chambre. Un carton est trop lourd. C'est trop difficile. Dorian va aller vers eux. Il va dire le besoin. Il appelle papa. Papa vient. Dorian dit le besoin : j'ai besoin d'aide. Maman n'est pas loin. Papa soulève le carton. Dorian dit merci. Demander, ce n'est pas être bébé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1486,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Dorian ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1659,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dorian a su aller vers eux. Il a su dire le besoin. Il a appelé papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1822,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose le carton. Dorian s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1989,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1310,6 +1315,7 @@
           <t>narrateur|Dorian est dans sa chambre. Un carton est trop lourd. C'est trop difficile. Dorian va aller vers eux. Il va dire le besoin. Il appelle papa. Papa vient. Dorian dit le besoin : j'ai besoin d'aide. Maman n'est pas loin. Papa soulève le carton. Dorian dit merci. Demander, ce n'est pas être bébé.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1499,7 @@
           <t>narrateur|C'est trop difficile. Que fait Dorian ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1664,6 +1671,7 @@
           <t>narrateur|Dorian a su aller vers eux. Il a su dire le besoin. Il a appelé papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1835,7 @@
           <t>narrateur|Papa pose le carton. Dorian s'assoit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2046,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2261,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dorian appelle papa</t>
+          <t>La chaussette d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une chaussette pend à l'armoire. Un carton de livres est trop lourd. Amir va vers papa et dit le besoin. Papa soulève le carton. Ils rangent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dorian est dans sa chambre. Un carton est trop lourd. C'est trop difficile. Dorian va aller vers eux. Il va dire le besoin. Il appelle papa. Papa vient. Dorian dit le besoin : j'ai besoin d'aide. Maman n'est pas loin. Papa soulève le carton. Dorian dit merci. Demander, ce n'est pas être bébé.</t>
+          <t>Une chaussette pend à l'armoire. L'armoire est un peu ouverte. Un rayon orange vient de la lampe. De la poussière danse dans le rayon. Le carton est au milieu de la chambre. Il est plein de livres. Ça sent le papier et le bois. Le tapis gris est un peu rêche. Maman plie un pull sur le lit. Papa cherche une place près de l'étagère. On range la chambre, Amir. Le carton va près des livres. En ce moment, Amir pose les mains sur le carton. Le carton est rêche et un peu poussiéreux. Je le pousse, papa. Tout doucement. Amir pousse un peu. Le carton bouge à peine. Il est trop lourd. C'est trop difficile. Il est trop lourd. Amir lâche le carton. Il va vers papa. Aller vers eux, c'est possible. Il va dire le besoin. Papa. J'ai besoin d'aide. Le carton est trop lourd. Je t'écoute, Amir. On le porte ensemble. Maman n'est pas loin. Tu as bien fait de le dire. Papa soulève le carton. Amir marche à côté, tout près. Ils posent le carton près de l'étagère. Ça fait un petit bruit sourd. Merci, papa. Bravo. Tu as dit le besoin. Demander, ce n'est pas être bébé. C'est aller vers eux. C'est dire le besoin. J'ai dit le besoin. Oui. C'est du bon travail. La chaussette pend encore. Tu ranges la chaussette ? Oui, maman. Amir prend la chaussette. Elle est molle et un peu chaude. Il la pose dans le tiroir. Merci, Amir. On ouvre le carton, maintenant ? Oui. Les livres. Amir sort un livre. La couverture est lisse et bleue. Tu le mets sur l'étagère ? Il est un peu haut. Amir se souvient. Il dit le besoin. Papa, j'ai besoin d'aide. Je t'écoute. Je le mets avec toi. Le livre bleu rejoint les autres. Le rayon orange est plus doux, maintenant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dorian est dans sa chambre. Un carton est trop lourd. C'est trop difficile. Dorian va aller vers eux. Il va dire le besoin. Il appelle papa. Papa vient. Dorian dit le besoin : j'ai besoin d'aide. Maman n'est pas loin. Papa soulève le carton. Dorian dit merci. Demander, ce n'est pas être bébé.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une chaussette pend à l'armoire.
+narrateur|L'armoire est un peu ouverte.
+narrateur|Un rayon orange vient de la lampe.
+narrateur|De la poussière danse dans le rayon.
+narrateur|Le carton est au milieu de la chambre.
+narrateur|Il est plein de livres.
+narrateur|Ça sent le papier et le bois.
+narrateur|Le tapis gris est un peu rêche.
+narrateur|Maman plie un pull sur le lit.
+narrateur|Papa cherche une place près de l'étagère.
+maman|On range la chambre, Amir.
+papa|Le carton va près des livres.
+narrateur|En ce moment, Amir pose les mains sur le carton.
+narrateur|Le carton est rêche et un peu poussiéreux.
+enfant-m|Je le pousse, papa.
+papa|Tout doucement.
+narrateur|Amir pousse un peu.
+narrateur|Le carton bouge à peine.
+narrateur|Il est trop lourd.
+narrateur|C'est trop difficile.
+enfant-m|Il est trop lourd.
+narrateur|Amir lâche le carton.
+narrateur|Il va vers papa.
+narrateur|Aller vers eux, c'est possible.
+narrateur|Il va dire le besoin.
+enfant-m|Papa. J'ai besoin d'aide.
+enfant-m|Le carton est trop lourd.
+papa|Je t'écoute, Amir.
+papa|On le porte ensemble.
+narrateur|Maman n'est pas loin.
+maman|Tu as bien fait de le dire.
+narrateur|Papa soulève le carton.
+narrateur|Amir marche à côté, tout près.
+narrateur|Ils posent le carton près de l'étagère.
+narrateur|Ça fait un petit bruit sourd.
+enfant-m|Merci, papa.
+papa|Bravo. Tu as dit le besoin.
+maman|Demander, ce n'est pas être bébé.
+papa|C'est aller vers eux.
+maman|C'est dire le besoin.
+enfant-m|J'ai dit le besoin.
+papa|Oui. C'est du bon travail.
+narrateur|La chaussette pend encore.
+maman|Tu ranges la chaussette ?
+enfant-m|Oui, maman.
+narrateur|Amir prend la chaussette.
+narrateur|Elle est molle et un peu chaude.
+narrateur|Il la pose dans le tiroir.
+maman|Merci, Amir.
+papa|On ouvre le carton, maintenant ?
+enfant-m|Oui. Les livres.
+narrateur|Amir sort un livre.
+narrateur|La couverture est lisse et bleue.
+papa|Tu le mets sur l'étagère ?
+enfant-m|Il est un peu haut.
+narrateur|Amir se souvient.
+narrateur|Il dit le besoin.
+enfant-m|Papa, j'ai besoin d'aide.
+papa|Je t'écoute. Je le mets avec toi.
+narrateur|Le livre bleu rejoint les autres.
+narrateur|Le rayon orange est plus doux, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1340,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>C'est trop difficile. Que fait Dorian ?</t>
+          <t>C'est trop difficile. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1496,10 +1567,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|C'est trop difficile. Que fait Dorian ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|C'est trop difficile.
+narrateur|Que fait Amir ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1524,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dorian a su aller vers eux. Il a su dire le besoin. Il a appelé papa.</t>
+          <t>Amir a su aller vers eux. Il a su dire le besoin. Il a appelé papa. Tu es venu me le dire. Bravo. C'est du bon travail, Amir. Tu as fini de ranger la chaussette ? Oui, maman. Le carton est à sa place. La poussière danse encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1668,10 +1739,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dorian a su aller vers eux. Il a su dire le besoin. Il a appelé papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a su aller vers eux.
+narrateur|Il a su dire le besoin.
+narrateur|Il a appelé papa.
+papa|Tu es venu me le dire.
+papa|Bravo.
+maman|C'est du bon travail, Amir.
+maman|Tu as fini de ranger la chaussette ?
+enfant-m|Oui, maman.
+narrateur|Le carton est à sa place.
+narrateur|La poussière danse encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1696,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa pose le carton. Dorian s'assoit.</t>
+          <t>Papa pose le carton. Amir s'assoit. Tu es fatigué ? Un peu, papa. Tu veux t'asseoir sur le tapis ? Oui. Le tapis gris est rêche sous les mains. Le livre bleu attend sur l'étagère. On reste encore un peu ensemble ? Oui, papa. La lampe fait un rond orange. L'armoire est fermée, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1832,10 +1911,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa pose le carton. Dorian s'assoit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa pose le carton.
+narrateur|Amir s'assoit.
+papa|Tu es fatigué ?
+enfant-m|Un peu, papa.
+maman|Tu veux t'asseoir sur le tapis ?
+enfant-m|Oui.
+narrateur|Le tapis gris est rêche sous les mains.
+narrateur|Le livre bleu attend sur l'étagère.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui, papa.
+narrateur|La lampe fait un rond orange.
+narrateur|L'armoire est fermée, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1860,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Amir. Tu as fait du bon travail. La chaussette est dans le tiroir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2000,10 +2089,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit le besoin.
+papa|Oui. Tu es venu vers moi.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+narrateur|La chaussette est dans le tiroir.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une chaussette pend à l'armoire. L'armoire est un peu ouverte. Un rayon orange vient de la lampe. De la poussière danse dans le rayon. Le carton est au milieu de la chambre. Il est plein de livres. Ça sent le papier et le bois. Le tapis gris est un peu rêche. Maman plie un pull sur le lit. Papa cherche une place près de l'étagère. On range la chambre, Amir. Le carton va près des livres. En ce moment, Amir pose les mains sur le carton. Le carton est rêche et un peu poussiéreux. Je le pousse, papa. Tout doucement. Amir pousse un peu. Le carton bouge à peine. Il est trop lourd. C'est trop difficile. Il est trop lourd. Amir lâche le carton. Il va vers papa. Aller vers eux, c'est possible. Il va dire le besoin. Papa. J'ai besoin d'aide. Le carton est trop lourd. Je t'écoute, Amir. On le porte ensemble. Maman n'est pas loin. Tu as bien fait de le dire. Papa soulève le carton. Amir marche à côté, tout près. Ils posent le carton près de l'étagère. Ça fait un petit bruit sourd. Merci, papa. Bravo. Tu as dit le besoin. Demander, ce n'est pas être bébé. C'est aller vers eux. C'est dire le besoin. J'ai dit le besoin. Oui. C'est du bon travail. La chaussette pend encore. Tu ranges la chaussette ? Oui, maman. Amir prend la chaussette. Elle est molle et un peu chaude. Il la pose dans le tiroir. Merci, Amir. On ouvre le carton, maintenant ? Oui. Les livres. Amir sort un livre. La couverture est lisse et bleue. Tu le mets sur l'étagère ? Il est un peu haut. Amir se souvient. Il dit le besoin. Papa, j'ai besoin d'aide. Je t'écoute. Je le mets avec toi. Le livre bleu rejoint les autres. Le rayon orange est plus doux, maintenant.</t>
+          <t>Une chaussette pend à l'armoire. L'armoire est un peu ouverte. Un rayon orange vient de la lampe. De la poussière danse dans le rayon. Le carton est au milieu de la chambre. Il est plein de livres. Ça sent le papier et le bois. Le tapis gris est un peu rêche. Maman plie un pull sur le lit. Papa cherche une place près de l'étagère. On range la chambre, Amir. Le carton va près des livres. En ce moment, Amir pose les mains sur le carton. Le carton est rêche et un peu poussiéreux. Je le pousse, papa. Tout doucement. Amir pousse un peu. Le carton bouge à peine. Il est trop lourd. C'est trop difficile. Il est trop lourd. Amir lâche le carton. Il va vers papa. Aller vers eux, c'est possible. Il va dire le besoin. Papa. J'ai besoin d'aide. Le carton est trop lourd. Je t'écoute, Amir. On le porte ensemble. Maman n'est pas loin. Tu as bien fait de le dire. Papa soulève le carton. Amir marche à côté, tout près. Ils posent le carton près de l'étagère. Ça fait un petit bruit sourd. Merci, papa. Bravo. Tu as dit le besoin. Demander, ce n'est pas être bébé. C'est aller vers eux. C'est dire le besoin. J'ai dit le besoin. La chaussette pend encore. Tu ranges la chaussette ? Oui, maman. Amir prend la chaussette. Elle est molle et un peu chaude. Il la pose dans le tiroir. Merci, Amir. On ouvre le carton, maintenant ? Oui. Les livres. Amir sort un livre. La couverture est lisse et bleue. Tu le mets sur l'étagère ? Il est un peu haut. Amir se souvient. Il dit le besoin. Papa, j'ai besoin d'aide. Je t'écoute. Je le mets avec toi. Le livre bleu rejoint les autres. Le rayon orange est plus doux, maintenant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dorian est dans sa chambre. Un carton est trop lourd. C'est trop difficile. Dorian va &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. Il va dire le besoin. Il appelle papa. Papa vient. Dorian dit le besoin : j'ai besoin d'aide. Maman n'est pas loin. Papa soulève le carton. Dorian dit merci. Demander, ce n'est pas être bébé.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une chaussette pend à l'armoire. L'armoire est un peu ouverte. Un rayon orange vient de la lampe. De la poussière danse dans le rayon. Le carton est au milieu de la chambre. Il est plein de livres. Ça sent le papier et le bois. Le tapis gris est un peu rêche. Maman plie un pull sur le lit. Papa cherche une place près de l'étagère. On range la chambre, Amir. Le carton va près des livres. En ce moment, Amir pose les mains sur le carton. Le carton est rêche et un peu poussiéreux. Je le pousse, papa. Tout doucement. Amir pousse un peu. Le carton bouge à peine. Il est trop lourd. C'est trop difficile. Il est trop lourd. Amir lâche le carton. Il va vers papa. Aller vers eux, c'est possible. Il va dire le besoin. Papa. J'ai besoin d'aide. Le carton est trop lourd. Je t'écoute, Amir. On le porte ensemble. Maman n'est pas loin. Tu as bien fait de le dire. Papa soulève le carton. Amir marche à côté, tout près. Ils posent le carton près de l'étagère. Ça fait un petit bruit sourd. Merci, papa. Bravo. Tu as dit le besoin. Demander, ce n'est pas être bébé. C'est aller vers eux. C'est dire le besoin. J'ai dit le besoin. La chaussette pend encore. Tu ranges la chaussette ? Oui, maman. Amir prend la chaussette. Elle est molle et un peu chaude. Il la pose dans le tiroir. Merci, Amir. On ouvre le carton, maintenant ? Oui. Les livres. Amir sort un livre. La couverture est lisse et bleue. Tu le mets sur l'étagère ? Il est un peu haut. Amir se souvient. Il dit le besoin. Papa, j'ai besoin d'aide. Je t'écoute. Je le mets avec toi. Le livre bleu rejoint les autres. Le rayon orange est plus doux, maintenant.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 papa|C'est aller vers eux.
 maman|C'est dire le besoin.
 enfant-m|J'ai dit le besoin.
-papa|Oui. C'est du bon travail.
 narrateur|La chaussette pend encore.
 maman|Tu ranges la chaussette ?
 enfant-m|Oui, maman.
@@ -1416,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est trop difficile. Que fait Dorian ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>C'est trop difficile. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a su aller vers eux. Il a su dire le besoin. Il a appelé papa. Tu es venu me le dire. Bravo. C'est du bon travail, Amir. Tu as fini de ranger la chaussette ? Oui, maman. Le carton est à sa place. La poussière danse encore un peu.</t>
+          <t>Amir a su aller vers eux. Il a su dire le besoin. Il a appelé papa. Tu es venu me le dire. Bravo. Tu as fini de ranger la chaussette ? Oui, maman. Le carton est à sa place. La poussière danse encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dorian a su &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. Il a su dire le besoin. Il a appelé papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a su aller vers eux. Il a su dire le besoin. Il a appelé papa. Tu es venu me le dire. Bravo. Tu as fini de ranger la chaussette ? Oui, maman. Le carton est à sa place. La poussière danse encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1743,6 @@
 narrateur|Il a appelé papa.
 papa|Tu es venu me le dire.
 papa|Bravo.
-maman|C'est du bon travail, Amir.
 maman|Tu as fini de ranger la chaussette ?
 enfant-m|Oui, maman.
 narrateur|Le carton est à sa place.
@@ -1780,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa pose le carton. Dorian s'assoit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose le carton. Amir s'assoit. Tu es fatigué ? Un peu, papa. Tu veux t'asseoir sur le tapis ? Oui. Le tapis gris est rêche sous les mains. Le livre bleu attend sur l'étagère. On reste encore un peu ensemble ? Oui, papa. La lampe fait un rond orange. L'armoire est fermée, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Amir. Tu as fait du bon travail. La chaussette est dans le tiroir. L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Amir. La chaussette est dans le tiroir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Amir. La chaussette est dans le tiroir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,9 +2090,7 @@
           <t>enfant-m|J'ai dit le besoin.
 papa|Oui. Tu es venu vers moi.
 maman|Bravo, Amir.
-maman|Tu as fait du bon travail.
-narrateur|La chaussette est dans le tiroir.
-narrateur|L'histoire est finie.</t>
+narrateur|La chaussette est dans le tiroir.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dorian, papa, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
